--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M04/run_3/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M04/run_3/CF_M04_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.5405</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.5517</v>
       </c>
       <c r="D3" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8784999999999999</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7577</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_03', 'AU_02', 'AU_16']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_39</t>
@@ -1233,7 +1245,6 @@
           <t>frontend, backend, authentication service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M04_AU01, CF_M04_AU21</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M04_AU21</t>
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.9006999999999999</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_03', 'AU_02', 'AU_16']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_38</t>
@@ -1315,7 +1323,6 @@
           <t>frontend, backend, authentication service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M04_AU04, CF_M04_AU18</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M04_AU19</t>
@@ -1365,7 +1371,6 @@
       <c r="D4" t="n">
         <v>0.9265</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1386,7 +1391,6 @@
           <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_41</t>
@@ -1397,7 +1401,6 @@
           <t>frontend, backend</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1416,7 +1419,6 @@
           <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M04_AU29</t>
@@ -1447,7 +1449,6 @@
       <c r="D5" t="n">
         <v>0.9288999999999999</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1468,7 +1469,6 @@
           <t>['AU_02', 'AU_13', 'AU_16']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_37</t>
@@ -1479,7 +1479,6 @@
           <t>backend, ai service, authentication service</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1498,7 +1497,6 @@
           <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M04_AU15</t>
@@ -1554,13 +1552,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Domain Layer</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M04_AU07</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1631,14 +1625,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -1662,13 +1653,11 @@
           <t>CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M04_AU11</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1709,14 +1698,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Firebase</t>
@@ -1735,14 +1721,11 @@
       <c r="P8" t="n">
         <v>56</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M04_AU27</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1788,13 +1771,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Infrastructure Layer</t>
@@ -1818,13 +1799,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1865,14 +1844,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Authentication Service</t>
@@ -1891,14 +1867,11 @@
       <c r="P10" t="n">
         <v>68</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M04_AU18</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1944,13 +1917,11 @@
           <t>['AU_35', 'AU_41']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -1974,13 +1945,11 @@
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M04_AU17</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2026,13 +1995,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Factory Pattern</t>
@@ -2056,13 +2023,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M04_P06</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2103,14 +2068,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -2129,14 +2091,11 @@
       <c r="P13" t="n">
         <v>55</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2182,13 +2141,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Application Layer</t>
@@ -2212,13 +2169,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M04_AU08</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2259,14 +2214,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -2285,14 +2237,11 @@
       <c r="P15" t="n">
         <v>54</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2338,13 +2287,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Django</t>
@@ -2368,13 +2315,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M04_AU05</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2420,13 +2365,11 @@
           <t>['AU_13']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gemini</t>
@@ -2445,14 +2388,11 @@
       <c r="P17" t="n">
         <v>55</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M04_AU14</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2498,13 +2438,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Repository Pattern</t>
@@ -2528,13 +2466,11 @@
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M04_P05</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2580,13 +2516,11 @@
           <t>['AU_13']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ChatGPT</t>
@@ -2605,14 +2539,11 @@
       <c r="P19" t="n">
         <v>55</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M04_AU13</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2653,14 +2584,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Hexagonal Architecture</t>
@@ -2686,13 +2614,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2733,14 +2659,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Flutter</t>
@@ -2764,13 +2687,11 @@
           <t>CF_M04_AU01, CF_M04_AU03</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2844,7 +2765,6 @@
           <t>Localboss</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Localboss, una start-up que desenvolupa una aplicació mòbil destinada a ajudar els propietaris de negocis a gestionar les seves ressenyes a Google Maps.</t>
@@ -2880,7 +2800,6 @@
           <t>Usuaris</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Usuaris: clients de l’aplicació que utilitzen les noves funcionalitats i proporcionen feedback.</t>
@@ -2916,7 +2835,6 @@
           <t>Competidors</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Competidors: altres aplicacions que ofereixen serveis similars de gestió de ressenyes a Google Maps.</t>
@@ -2952,7 +2870,6 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Una start-up que desenvolupa una aplicació mòbil destinada a ajudar els propietaris de negocis a gestionar les seves ressenyes a Google Maps.</t>
@@ -2988,7 +2905,6 @@
           <t>AI Service</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Finalment, el sistema integra diversos serveis externs a través del back-end, com ara serveis d’intel·ligència artificial (Gemini o ChatGPT) i serveis d’autenticació.</t>
@@ -2999,7 +2915,6 @@
           <t>CF_M04_AU15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.7329</v>
       </c>
@@ -3020,7 +2935,6 @@
           <t>Google OAuth 2.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Presenta les opcions d'autenticació disponibles, destacant el mètode principal mitjançant Google OAuth 2.0.</t>
@@ -3056,7 +2970,6 @@
           <t>Jira</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Jira per a la gestió de requisits i tasques.</t>
@@ -3092,7 +3005,6 @@
           <t>Git</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Git com a sistema de control de versions.</t>
@@ -3128,7 +3040,6 @@
           <t>Android Studio</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Android Studio i VS Code com a entorns de desenvolupament.</t>
@@ -3164,7 +3075,6 @@
           <t>VS Code</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Android Studio i VS Code com a entorns de desenvolupament.</t>
@@ -3200,7 +3110,6 @@
           <t>Dart</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Front-End: Flutter (Dart), utilitzat per al desenvolupament multiplataforma de l’aplicació mòbil per a Android i iOS.</t>
@@ -3236,7 +3145,6 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Back-End: Django (Python), utilitzat com a framework principal per a la construcció de l’API REST.</t>
@@ -3272,7 +3180,6 @@
           <t>Android</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Front-End: Flutter (Dart), utilitzat per al desenvolupament multiplataforma de l’aplicació mòbil per a Android i iOS.</t>
@@ -3308,7 +3215,6 @@
           <t>iOS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Front-End: Flutter (Dart), utilitzat per al desenvolupament multiplataforma de l’aplicació mòbil per a Android i iOS.</t>
@@ -3344,7 +3250,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Les dades s’intercanvien en format JSON, utilitzant mètodes HTTP estàndard com GET i POST.</t>
@@ -3355,7 +3260,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0.7808</v>
       </c>
@@ -3376,7 +3280,6 @@
           <t>syncfusion_flutter_charts</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>syncfusion_flutter_charts: utilitzada per a la creació de gràfics avançats a la nova pantalla Home</t>
@@ -3412,7 +3315,6 @@
           <t>fl_chart</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>fl_chart: emprada per a la implementació de gràfics lineals</t>
@@ -3448,7 +3350,6 @@
           <t>SliverAppBar</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>SliverAppBar: utilitzada per implementar una App Bar avançada</t>
@@ -3484,7 +3385,6 @@
           <t>video_player</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>video_player: incorporada per permetre la reproducció de vídeos associats a les reviews.</t>
@@ -3520,7 +3420,6 @@
           <t>Postman</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Postman per provar i validar els endpoints del backend abans de la seva integració al front-end.</t>
@@ -3551,7 +3450,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>backend, frontend</t>
@@ -3587,7 +3485,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -3603,7 +3500,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0.8879</v>
       </c>
@@ -3619,7 +3515,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>backend, mysql</t>
@@ -3655,7 +3550,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>frontend, backend, ai service</t>
@@ -3671,7 +3565,6 @@
           <t>CF_M04_AU15</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0.7279</v>
       </c>
@@ -3692,7 +3585,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Des del punt de vista de l’usuari, la interacció amb el sistema es realitza a través d’una aplicació mòbil desenvolupada amb Flutter, que actua com a capa de presentació (front-end)... realitzar les peticions necessàries al back-end per obtenir o modificar informació.</t>
@@ -3728,7 +3620,6 @@
           <t>Dependency Injection</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Inversió de Dependència (DIP): El domini defineix interfícies que són implementades per la infraestructura.</t>
@@ -3820,7 +3711,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
@@ -3856,7 +3746,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Communication between the front-end and the back-end is done through a REST API</t>
@@ -3892,7 +3781,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
@@ -3923,7 +3811,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>application layer, domain layer, infrastructure layer</t>
@@ -3959,7 +3846,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>infrastructure layer, gemini</t>
@@ -3975,7 +3861,6 @@
           <t>AU_37</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.8408</v>
       </c>
@@ -3996,7 +3881,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Users: Application customers who use the new features and provide feedback.</t>
@@ -4032,7 +3916,6 @@
           <t>Domain</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Domain: contains the business logic, with use cases, entities and repositories defined as interfaces.</t>
@@ -4068,7 +3951,6 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
@@ -4104,7 +3986,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
@@ -4135,7 +4016,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>backend, database</t>
@@ -4151,7 +4031,6 @@
           <t>AU_35</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0.7403999999999999</v>
       </c>
@@ -4172,7 +4051,6 @@
           <t>Google Login</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Authentication services, such as Google login.</t>
@@ -4203,7 +4081,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -4244,7 +4121,6 @@
           <t>Hierarchical model</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
@@ -4280,7 +4156,6 @@
           <t>Modular architecture</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
@@ -4316,7 +4191,6 @@
           <t>Bloc/Cubit</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
@@ -4352,7 +4226,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
@@ -4363,7 +4236,6 @@
           <t>AU_36</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0.7435</v>
       </c>
@@ -4384,7 +4256,6 @@
           <t>Clean Architecture</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>The front-end is implemented with Flutter and follows a structure based on the principles of Clean Architecture, strictly applied.</t>
